--- a/SGC-CKN/Excel/d6f6eaab-170f-405a-8781-53842685e82c_Thi_công_cọc_khoan_nhồi__tường_vây_cho_các_hạng_mục_Lô_CT-02_P1-18_D800_22-04-2026.xlsx
+++ b/SGC-CKN/Excel/d6f6eaab-170f-405a-8781-53842685e82c_Thi_công_cọc_khoan_nhồi__tường_vây_cho_các_hạng_mục_Lô_CT-02_P1-18_D800_22-04-2026.xlsx
@@ -92,7 +92,7 @@
     <t>Đất thổ nhưỡng</t>
   </si>
   <si>
-    <t xml:space="preserve">17:30
+    <t xml:space="preserve">17:10
 21/04/2026</t>
   </si>
   <si>
@@ -231,7 +231,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -262,18 +262,12 @@
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFC2410C"/>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
       <color rgb="FF78350F"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <color rgb="FFC2410C"/>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
@@ -320,7 +314,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -349,7 +343,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC2626"/>
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -375,11 +369,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDD6FE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -490,7 +479,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -525,38 +514,44 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -576,22 +571,13 @@
     <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1183,13 +1169,13 @@
         <v>-0.6</v>
       </c>
       <c r="H11" s="5">
-        <v>23.83</v>
+        <v>0.17</v>
       </c>
       <c r="I11" s="5">
         <v>0.6</v>
       </c>
       <c r="J11" s="8">
-        <v>0.03</v>
+        <v>3.6</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>28</v>
@@ -1328,7 +1314,7 @@
       <c r="I15" s="19">
         <v>6.52</v>
       </c>
-      <c r="J15" s="22">
+      <c r="J15" s="8">
         <v>4.89</v>
       </c>
       <c r="K15" s="20" t="s">
@@ -1336,124 +1322,124 @@
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="24" t="s">
+      <c r="C16" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="D16" s="25" t="s">
+      <c r="D16" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="E16" s="25" t="s">
+      <c r="E16" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="F16" s="23">
+      <c r="F16" s="22">
         <v>-22.52</v>
       </c>
-      <c r="G16" s="23">
+      <c r="G16" s="22">
         <v>-26.42</v>
       </c>
-      <c r="H16" s="23">
+      <c r="H16" s="22">
         <v>1.4</v>
       </c>
-      <c r="I16" s="23">
+      <c r="I16" s="22">
         <v>3.9</v>
       </c>
-      <c r="J16" s="22">
+      <c r="J16" s="8">
         <v>2.79</v>
       </c>
-      <c r="K16" s="24" t="s">
+      <c r="K16" s="23" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="26" t="s">
+      <c r="A17" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="B17" s="26" t="s">
+      <c r="B17" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="27" t="s">
+      <c r="C17" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="D17" s="28" t="s">
+      <c r="D17" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="E17" s="28" t="s">
+      <c r="E17" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="F17" s="26">
+      <c r="F17" s="25">
         <v>-26.42</v>
       </c>
-      <c r="G17" s="26">
+      <c r="G17" s="25">
         <v>-39.5</v>
       </c>
-      <c r="H17" s="26">
+      <c r="H17" s="25">
         <v>1.65</v>
       </c>
-      <c r="I17" s="26">
+      <c r="I17" s="25">
         <v>13.08</v>
       </c>
       <c r="J17" s="12">
         <v>7.93</v>
       </c>
-      <c r="K17" s="27" t="s">
+      <c r="K17" s="26" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="29" t="s">
+      <c r="A18" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="B18" s="29" t="s">
+      <c r="B18" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="30" t="s">
+      <c r="C18" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="D18" s="31" t="s">
+      <c r="D18" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="E18" s="31" t="s">
+      <c r="E18" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="F18" s="29">
+      <c r="F18" s="28">
         <v>-39.5</v>
       </c>
-      <c r="G18" s="29">
+      <c r="G18" s="28">
         <v>-44.65</v>
       </c>
-      <c r="H18" s="29">
+      <c r="H18" s="28">
         <v>2.75</v>
       </c>
-      <c r="I18" s="29">
+      <c r="I18" s="28">
         <v>5.15</v>
       </c>
-      <c r="J18" s="22">
+      <c r="J18" s="8">
         <v>1.87</v>
       </c>
-      <c r="K18" s="30" t="s">
+      <c r="K18" s="29" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="32" t="s">
+      <c r="A21" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="B21" s="32"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="32"/>
-      <c r="K21" s="32"/>
+      <c r="B21" s="31"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="31"/>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="31"/>
     </row>
     <row r="22" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1595,13 +1581,13 @@
         <v>-0.6</v>
       </c>
       <c r="G2" s="5">
-        <v>23.83</v>
+        <v>0.17</v>
       </c>
       <c r="H2" s="5">
         <v>0.6</v>
       </c>
       <c r="I2" s="8">
-        <v>0.03</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1716,62 +1702,62 @@
       <c r="H6" s="19">
         <v>6.52</v>
       </c>
-      <c r="I6" s="22">
+      <c r="I6" s="8">
         <v>4.89</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="23">
+      <c r="A7" s="22">
         <v>6</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="D7" s="23">
+      <c r="D7" s="22">
         <v>1</v>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="22">
         <v>-22.52</v>
       </c>
-      <c r="F7" s="23">
+      <c r="F7" s="22">
         <v>-26.42</v>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="22">
         <v>1.4</v>
       </c>
-      <c r="H7" s="23">
+      <c r="H7" s="22">
         <v>3.9</v>
       </c>
-      <c r="I7" s="22">
+      <c r="I7" s="8">
         <v>2.79</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="26">
+      <c r="A8" s="25">
         <v>7</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="27" t="s">
+      <c r="C8" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="25">
         <v>1</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="25">
         <v>-26.42</v>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="25">
         <v>-39.5</v>
       </c>
-      <c r="G8" s="26">
+      <c r="G8" s="25">
         <v>1.65</v>
       </c>
-      <c r="H8" s="26">
+      <c r="H8" s="25">
         <v>13.08</v>
       </c>
       <c r="I8" s="12">
@@ -1779,61 +1765,61 @@
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="29">
+      <c r="A9" s="28">
         <v>8</v>
       </c>
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="30" t="s">
+      <c r="C9" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="28">
         <v>1</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="28">
         <v>-39.5</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="28">
         <v>-44.65</v>
       </c>
-      <c r="G9" s="29">
+      <c r="G9" s="28">
         <v>2.75</v>
       </c>
-      <c r="H9" s="29">
+      <c r="H9" s="28">
         <v>5.15</v>
       </c>
-      <c r="I9" s="22">
+      <c r="I9" s="8">
         <v>1.87</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="33" t="s">
+      <c r="A10" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="B10" s="34" t="s">
+      <c r="B10" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="C10" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="34">
+      <c r="D10" s="33">
         <v>8</v>
       </c>
-      <c r="E10" s="34">
+      <c r="E10" s="33">
         <v>0</v>
       </c>
-      <c r="F10" s="34">
+      <c r="F10" s="33">
         <v>-44.65</v>
       </c>
-      <c r="G10" s="34">
-        <v>32.37</v>
-      </c>
-      <c r="H10" s="34">
+      <c r="G10" s="33">
+        <v>8.7</v>
+      </c>
+      <c r="H10" s="33">
         <v>44.65</v>
       </c>
-      <c r="I10" s="34">
-        <v>1.38</v>
+      <c r="I10" s="33">
+        <v>5.13</v>
       </c>
     </row>
   </sheetData>

--- a/SGC-CKN/Excel/d6f6eaab-170f-405a-8781-53842685e82c_Thi_công_cọc_khoan_nhồi__tường_vây_cho_các_hạng_mục_Lô_CT-02_P1-18_D800_22-04-2026.xlsx
+++ b/SGC-CKN/Excel/d6f6eaab-170f-405a-8781-53842685e82c_Thi_công_cọc_khoan_nhồi__tường_vây_cho_các_hạng_mục_Lô_CT-02_P1-18_D800_22-04-2026.xlsx
@@ -50,13 +50,13 @@
     <t>Bắt đầu thi công</t>
   </si>
   <si>
-    <t>17:10 21/04/2026</t>
+    <t>17:10 02/04/2026</t>
   </si>
   <si>
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>02:10 22/04/2026</t>
+    <t>02:10 03/04/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -93,11 +93,11 @@
   </si>
   <si>
     <t xml:space="preserve">17:10
-21/04/2026</t>
+02/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">17:20
-21/04/2026</t>
+02/04/2026</t>
   </si>
   <si>
     <t/>
@@ -110,11 +110,11 @@
   </si>
   <si>
     <t xml:space="preserve">17:22
-21/04/2026</t>
+02/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">17:48
-21/04/2026</t>
+02/04/2026</t>
   </si>
   <si>
     <t>3</t>
@@ -124,11 +124,11 @@
   </si>
   <si>
     <t xml:space="preserve">18:42
-21/04/2026</t>
+02/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">18:55
-21/04/2026</t>
+02/04/2026</t>
   </si>
   <si>
     <t>4</t>
@@ -138,11 +138,11 @@
   </si>
   <si>
     <t xml:space="preserve">18:00
-21/04/2026</t>
+02/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">18:45
-21/04/2026</t>
+02/04/2026</t>
   </si>
   <si>
     <t>5</t>
@@ -152,11 +152,11 @@
   </si>
   <si>
     <t xml:space="preserve">19:00
-21/04/2026</t>
+02/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">20:20
-21/04/2026</t>
+02/04/2026</t>
   </si>
   <si>
     <t>6</t>
@@ -166,11 +166,11 @@
   </si>
   <si>
     <t xml:space="preserve">20:21
-21/04/2026</t>
+02/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">21:45
-21/04/2026</t>
+02/04/2026</t>
   </si>
   <si>
     <t>7</t>
@@ -180,11 +180,11 @@
   </si>
   <si>
     <t xml:space="preserve">21:46
-21/04/2026</t>
+02/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">23:25
-21/04/2026</t>
+02/04/2026</t>
   </si>
   <si>
     <t>8</t>
@@ -194,7 +194,7 @@
   </si>
   <si>
     <t xml:space="preserve">02:10
-21/04/2026</t>
+02/04/2026</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>

--- a/SGC-CKN/Excel/d6f6eaab-170f-405a-8781-53842685e82c_Thi_công_cọc_khoan_nhồi__tường_vây_cho_các_hạng_mục_Lô_CT-02_P1-18_D800_22-04-2026.xlsx
+++ b/SGC-CKN/Excel/d6f6eaab-170f-405a-8781-53842685e82c_Thi_công_cọc_khoan_nhồi__tường_vây_cho_các_hạng_mục_Lô_CT-02_P1-18_D800_22-04-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="64">
   <si>
     <t>Dự án</t>
   </si>
@@ -113,7 +113,7 @@
 02/04/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">17:48
+    <t xml:space="preserve">17:42
 02/04/2026</t>
   </si>
   <si>
@@ -121,26 +121,18 @@
   </si>
   <si>
     <t>Cát pha xám ghi, xám nâu TT dẻo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18:42
-02/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18:55
-02/04/2026</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>Sét xám trắng, xám xanh dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">18:00
 02/04/2026</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Sét xám trắng, xám xanh dẻo chảy</t>
+  </si>
+  <si>
     <t xml:space="preserve">18:45
 02/04/2026</t>
   </si>
@@ -194,7 +186,7 @@
   </si>
   <si>
     <t xml:space="preserve">02:10
-02/04/2026</t>
+03/04/2026</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>
@@ -1204,13 +1196,13 @@
         <v>-3.7</v>
       </c>
       <c r="H12" s="9">
-        <v>0.43</v>
+        <v>0.33</v>
       </c>
       <c r="I12" s="9">
         <v>3.1</v>
       </c>
       <c r="J12" s="12">
-        <v>7.15</v>
+        <v>9.3</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>28</v>
@@ -1227,10 +1219,10 @@
         <v>34</v>
       </c>
       <c r="D13" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" s="15" t="s">
         <v>35</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>36</v>
       </c>
       <c r="F13" s="13">
         <v>-3.7</v>
@@ -1239,13 +1231,13 @@
         <v>-7.2</v>
       </c>
       <c r="H13" s="13">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="I13" s="13">
         <v>3.5</v>
       </c>
       <c r="J13" s="12">
-        <v>16.15</v>
+        <v>11.67</v>
       </c>
       <c r="K13" s="14" t="s">
         <v>28</v>
@@ -1253,19 +1245,19 @@
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>10</v>
       </c>
       <c r="C14" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" s="18" t="s">
         <v>38</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>40</v>
       </c>
       <c r="F14" s="16">
         <v>-7.2</v>
@@ -1288,19 +1280,19 @@
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>10</v>
       </c>
       <c r="C15" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="E15" s="21" t="s">
         <v>42</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="E15" s="21" t="s">
-        <v>44</v>
       </c>
       <c r="F15" s="19">
         <v>-16</v>
@@ -1323,19 +1315,19 @@
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B16" s="22" t="s">
         <v>10</v>
       </c>
       <c r="C16" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" s="24" t="s">
         <v>46</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="E16" s="24" t="s">
-        <v>48</v>
       </c>
       <c r="F16" s="22">
         <v>-22.52</v>
@@ -1358,19 +1350,19 @@
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B17" s="25" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="E17" s="27" t="s">
         <v>50</v>
-      </c>
-      <c r="D17" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="E17" s="27" t="s">
-        <v>52</v>
       </c>
       <c r="F17" s="25">
         <v>-26.42</v>
@@ -1393,19 +1385,19 @@
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B18" s="28" t="s">
         <v>10</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D18" s="30" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E18" s="30" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F18" s="28">
         <v>-39.5</v>
@@ -1428,7 +1420,7 @@
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="31" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B21" s="31"/>
       <c r="C21" s="31"/>
@@ -1534,31 +1526,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1610,13 +1602,13 @@
         <v>-3.7</v>
       </c>
       <c r="G3" s="9">
-        <v>0.43</v>
+        <v>0.33</v>
       </c>
       <c r="H3" s="9">
         <v>3.1</v>
       </c>
       <c r="I3" s="12">
-        <v>7.15</v>
+        <v>9.3</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1639,13 +1631,13 @@
         <v>-7.2</v>
       </c>
       <c r="G4" s="13">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="H4" s="13">
         <v>3.5</v>
       </c>
       <c r="I4" s="12">
-        <v>16.15</v>
+        <v>11.67</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1656,7 +1648,7 @@
         <v>10</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D5" s="16">
         <v>1</v>
@@ -1685,7 +1677,7 @@
         <v>10</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D6" s="19">
         <v>1</v>
@@ -1714,7 +1706,7 @@
         <v>10</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D7" s="22">
         <v>1</v>
@@ -1743,7 +1735,7 @@
         <v>10</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
@@ -1772,7 +1764,7 @@
         <v>10</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
@@ -1795,7 +1787,7 @@
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B10" s="33" t="s">
         <v>28</v>
@@ -1813,13 +1805,13 @@
         <v>-44.65</v>
       </c>
       <c r="G10" s="33">
-        <v>8.7</v>
+        <v>8.68</v>
       </c>
       <c r="H10" s="33">
         <v>44.65</v>
       </c>
       <c r="I10" s="33">
-        <v>5.13</v>
+        <v>5.14</v>
       </c>
     </row>
   </sheetData>
